--- a/dataset_t6_grouped/results2/G3/G3_T0801_W0022F0002T0006Z000C1N37_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G3/G3_T0801_W0022F0002T0006Z000C1N37_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>43.57227282208765</v>
+        <v>7.080494333589244</v>
       </c>
       <c r="D2" t="n">
-        <v>44.16106276586755</v>
+        <v>7.176172699453477</v>
       </c>
       <c r="E2" t="n">
-        <v>18.00327717945559</v>
+        <v>2.925532541661533</v>
       </c>
       <c r="F2" t="n">
-        <v>13.56814864936833</v>
+        <v>2.204824155522354</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>17.7795138041261</v>
+        <v>2.889170993170492</v>
       </c>
       <c r="D3" t="n">
-        <v>32.65565823936964</v>
+        <v>5.306544463897566</v>
       </c>
       <c r="E3" t="n">
-        <v>18.00327717945559</v>
+        <v>2.925532541661533</v>
       </c>
       <c r="F3" t="n">
-        <v>13.56814864936833</v>
+        <v>2.204824155522354</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>45.224440295044</v>
+        <v>7.348971547944651</v>
       </c>
       <c r="D4" t="n">
-        <v>59.61253258333455</v>
+        <v>9.687036544791864</v>
       </c>
       <c r="E4" t="n">
-        <v>18.00327717945559</v>
+        <v>2.925532541661533</v>
       </c>
       <c r="F4" t="n">
-        <v>13.56814864936833</v>
+        <v>2.204824155522354</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>61.08650632466632</v>
+        <v>9.926557277758278</v>
       </c>
       <c r="D5" t="n">
-        <v>61.63191389645646</v>
+        <v>10.01518600817418</v>
       </c>
       <c r="E5" t="n">
-        <v>18.00327717945559</v>
+        <v>2.925532541661533</v>
       </c>
       <c r="F5" t="n">
-        <v>13.56814864936833</v>
+        <v>2.204824155522354</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>72.91257556609206</v>
+        <v>11.84829352948996</v>
       </c>
       <c r="D6" t="n">
-        <v>73.56397052565175</v>
+        <v>11.95414521041841</v>
       </c>
       <c r="E6" t="n">
-        <v>18.00327717945559</v>
+        <v>2.925532541661533</v>
       </c>
       <c r="F6" t="n">
-        <v>13.56814864936833</v>
+        <v>2.204824155522354</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>64.07606836874581</v>
+        <v>10.41236110992119</v>
       </c>
       <c r="D7" t="n">
-        <v>64.13614226643037</v>
+        <v>10.42212311829494</v>
       </c>
       <c r="E7" t="n">
-        <v>18.00327717945559</v>
+        <v>2.925532541661533</v>
       </c>
       <c r="F7" t="n">
-        <v>13.56814864936833</v>
+        <v>2.204824155522354</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
